--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92316</v>
+        <v>92319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
